--- a/outputs/식이_개발전달_20260923/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/식이_개발전달_20260923/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -2,31 +2,32 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R61536df0889a4f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블정의" sheetId="2" r:id="R85fe56cfea9d48f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="필드정의" sheetId="3" r:id="R2ba9571ee7224ed2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정필요" sheetId="4" r:id="R3fc544cda4264986"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질문" sheetId="5" r:id="R236c2977a628432f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택지" sheetId="6" r:id="Rb86d6d09607b4cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목표문구" sheetId="7" r:id="R065960e790ec47e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="노출조건" sheetId="8" r:id="R6e9bd4b072124278"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환규칙" sheetId="9" r:id="R44929427aa194b6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환연결축" sheetId="10" r:id="Rd0019a53cb6d4c1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환금지성격" sheetId="11" r:id="R3695a72d5ded49cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드조건" sheetId="12" r:id="R0eeba39807f54852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정" sheetId="13" r:id="R53830f2ace8e4c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정파라미터" sheetId="14" r:id="R3eda6dcfe6cb4533"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진출처" sheetId="15" r:id="R462178cbdf5440c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진항목" sheetId="16" r:id="R7d7d67317caa4c2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진성분규격" sheetId="17" r:id="Rf34ffe7ac5c941cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정그룹" sheetId="18" r:id="R83820819ae9846b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정조건" sheetId="19" r:id="R5e6803237357415a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진범주코드" sheetId="20" r:id="R6e9506e6b33a4721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진적용정책" sheetId="21" r:id="R498fa8b7865a4018"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진보조기준" sheetId="22" r:id="R1bb4de5c8c7841a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진식이연결" sheetId="23" r:id="R4c0de528305e4589"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="또래등수정책" sheetId="24" r:id="Ra07bb30b256c4afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증규칙" sheetId="25" r:id="R8fa4425ab5264e9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R07f5985abccc41d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블정의" sheetId="2" r:id="Rbcaef21fd09e495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="필드정의" sheetId="3" r:id="R7b5df505806846b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결정필요" sheetId="4" r:id="R7786cbd13c5043d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질문" sheetId="5" r:id="Rc669aee1b70847ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택지" sheetId="6" r:id="R81d33d5784964525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목표문구" sheetId="7" r:id="Rb26e91a628914e47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="노출조건" sheetId="8" r:id="Rfccb793bd26f43d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환규칙" sheetId="9" r:id="R55da10cd1faf4c42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환연결축" sheetId="10" r:id="R3a4459e5bc32403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질환금지성격" sheetId="11" r:id="R29435c4c590148f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드조건" sheetId="12" r:id="Rf77fe9867a42469b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정" sheetId="13" r:id="Rf90be589a98c402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정파라미터" sheetId="14" r:id="R83fb64ff9c8044cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진출처" sheetId="15" r:id="R7b651466f44c4804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진항목" sheetId="16" r:id="R67dcc7506bb8482e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진성분규격" sheetId="17" r:id="Rcc61e57e7aae46a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정그룹" sheetId="18" r:id="Rea5e6faded324c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진판정조건" sheetId="19" r:id="Re88596324dd34a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진범주코드" sheetId="20" r:id="Rd51672e902804cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진적용정책" sheetId="21" r:id="R8a50fea2d5394182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진보조기준" sheetId="22" r:id="R2bdf8dc70ac04eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검진식이연결" sheetId="23" r:id="R32c520383ff742c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="또래등수정책" sheetId="24" r:id="R2e39c2b55adf4294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증규칙" sheetId="25" r:id="Raa1055405cf74070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="내정보질환매핑" sheetId="26" r:id="Rfe89ef40c2d041ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5111,7 +5112,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -5135,8 +5136,13 @@
       <x:sz val="8"/>
       <x:name val="돋움"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1D2B3A"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -5153,6 +5159,11 @@
         <x:fgColor rgb="FFFFF4E5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF245A7A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -5161,7 +5172,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -5183,6 +5194,9 @@
     <x:xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -5372,7 +5386,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DietTableDef" displayName="DietTableDef" ref="A1:G34" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="DietTableDef" displayName="DietTableDef" ref="A1:G37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="테이블명"/>
     <x:tableColumn id="2" name="데이터 시트"/>
@@ -5461,7 +5475,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="규칙 ID"/>
     <x:tableColumn id="2" name="대상"/>
@@ -5472,8 +5486,22 @@
 </x:table>
 </file>
 
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="DietProfileConditionMap" displayName="DietProfileConditionMap" ref="A1:F13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="condition_code"/>
+    <x:tableColumn id="2" name="display_name"/>
+    <x:tableColumn id="3" name="diet_status"/>
+    <x:tableColumn id="4" name="rule_id"/>
+    <x:tableColumn id="5" name="mapping_note"/>
+    <x:tableColumn id="6" name="source_ui"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="DietFieldDef" displayName="DietFieldDef" ref="A1:I274" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="DietFieldDef" displayName="DietFieldDef" ref="A1:I288" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="테이블명"/>
     <x:tableColumn id="2" name="순서"/>
@@ -5490,7 +5518,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="DietOpenIssues" displayName="DietOpenIssues" ref="A1:G16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="DietOpenIssues" displayName="DietOpenIssues" ref="A1:G17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="이슈 ID"/>
     <x:tableColumn id="2" name="우선순위"/>
@@ -5916,7 +5944,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1227c1e8691348e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1b95f96b1344f92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6151,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f2cc99f10f041e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e4c945ffb284545"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6451,7 +6479,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdf416c08fbc4310"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R654ebe8fc9284756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8530,7 +8558,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99bb90cf81e54a8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9502e9cecf54642"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10246,7 +10274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36335cf9e36941dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93bdd6476d7546ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10641,7 +10669,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57a83faeec964990"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74f04d52a2a741de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10838,7 +10866,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc944539f83f4c9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3ee53335a5748e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11275,7 +11303,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96903397fb734701"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f2d3e98cf544492"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11636,7 +11664,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f8d7210fb1430d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79a795446204767"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13226,7 +13254,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fd87ba0406b4c17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccaf1167cb0548f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14806,7 +14834,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07166532a3c54d8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5db0895b8ebc43b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15609,10 +15637,79 @@
         <x:v>200</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>내정보질환매핑</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>참조</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>화면 질환 코드</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>condition_code</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>수동 선택지 12개와 식이 규칙 연결 상태</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>MAPPED만 자동 연결. UNMAPPED·NEEDS_SUBTYPE은 입력 보존, 식이 규칙 적용 보류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>user_condition_response</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>정의만 제공</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>런타임</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>사용자 + 응답 리비전</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>user_id,revision</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>수동 입력의 미응답·해당 없음·선택 상태와 저장 시각</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>진료정보 확인 상태와 별도 보관; 최신 리비전만 현재 입력으로 사용</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>user_condition_selection</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>정의만 제공</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>런타임</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>사용자 + 응답 리비전 + 질환 코드</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>user_id,revision,condition_code</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>해당 리비전에서 사용자가 선택한 질환 코드</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>NONE 리비전에는 선택 행 0개. 해제 시 진료정보 행을 수정하지 않음</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0199ca87a2484dbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a4e7c7571e4472d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15701,7 +15798,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3efac503b614fbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b77430dee3e4ac2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15922,7 +16019,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc299388dd384097"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R962d8ba1fa054b37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16778,7 +16875,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0247aceef9942f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R312b20804510493a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16943,7 +17040,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbe5a8aabd0e41fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1990db46a14937"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17136,7 +17233,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ef1a95324a44f8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3923f160661e48b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17630,10 +17727,339 @@
         <x:v>00~04시와 04~10시에 같은 (user_id,meal_date,meal_type,question_id,question_version)의 유효 답이 있으면 재질문·재집계하지 않는다. 각 세션의 ANSWERED 문항 상태 effective_answer_id는 그 유효 답을 참조한다. 유효 답이 없을 때만 질문; 식후 후보가 없으면 GUIDANCE_ONLY</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>V-35</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>내정보질환매핑</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>화면의 12개 질환 코드가 유일하고 MAPPED는 존재하는 질환규칙을 참조</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>정의되지 않은 코드·중복 코드·없는 규칙 ID 적재 거부</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>V-36</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>수동 질환 입력</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>SELF_REPORTED는 진료정보 출처·임상 확진으로 승격하지 않음. MAPPED만 연결 축·금지 성격 적용</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>UNMAPPED·NEEDS_SUBTYPE의 식이 자동 연결 금지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>V-37</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>수동 입력과 진료정보</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>NONE은 수동 선택 0개로 저장하고 UNANSWERED와 구분. 진료정보 후보·확인·부정 원본은 별도 보존</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>해당 없음 선택이나 수동 해제로 진료정보 상태 삭제 금지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>V-38</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>질환 변경 후 목표</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>새 입력은 당일 미완료 목표 후보를 안전 필터로 재평가. 완료 목표와 과거 스냅샷은 보존</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>재선정한 대체 후보에도 금지·시간·상황 조건 재적용. 후보 0개면 안내 상태</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f70ecd3f3fe4b36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R217374f3c4154b91"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="27" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="63" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="53" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="68" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="8" t="str">
+        <x:v>condition_code</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
+        <x:v>display_name</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="str">
+        <x:v>diet_status</x:v>
+      </x:c>
+      <x:c r="D1" s="8" t="str">
+        <x:v>rule_id</x:v>
+      </x:c>
+      <x:c r="E1" s="8" t="str">
+        <x:v>mapping_note</x:v>
+      </x:c>
+      <x:c r="F1" s="8" t="str">
+        <x:v>source_ui</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>화면 출처</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>HYPERTENSION</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>고혈압</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>MAPPED</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>DX-02</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>동일 질환명과 기존 연결 축 확인</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>https://srleeinkorea.github.io/maireport-rsna-demo-k7x9m2q8v4n6/#prototype</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="6" t="str">
+        <x:v>DIABETES</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>당뇨병</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>MAPPED</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>DX-01</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>동일 질환명과 기존 금지 성격 확인</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>DYSLIPIDEMIA</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>이상지질혈증</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>MAPPED</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>DX-03</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>고중성지방 세부형 DX-04는 자동 추정하지 않음</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="6" t="str">
+        <x:v>CHRONIC_KIDNEY_DISEASE</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>만성 신장질환</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>MAPPED</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>DX-05</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>동일 질환명과 기존 금지 성격 확인</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="6" t="str">
+        <x:v>OBESITY</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>비만</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>UNMAPPED</x:v>
+      </x:c>
+      <x:c r="D6" s="6"/>
+      <x:c r="E6" s="6" t="str">
+        <x:v>자가 선택을 BMI 25 이상 검진 수치로 대체하지 않음</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="6" t="str">
+        <x:v>FATTY_LIVER</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>지방간</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>MAPPED</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>DX-07</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>동일 질환명과 기존 연결 축 확인</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="6" t="str">
+        <x:v>GERD</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>위식도역류병</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>UNMAPPED</x:v>
+      </x:c>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>식이 질환규칙 없음</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="6" t="str">
+        <x:v>GOUT</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>통풍</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>UNMAPPED</x:v>
+      </x:c>
+      <x:c r="D9" s="6"/>
+      <x:c r="E9" s="6" t="str">
+        <x:v>식이 질환규칙 없음</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="str">
+        <x:v>THYROID_DISEASE</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>갑상선 질환</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>UNMAPPED</x:v>
+      </x:c>
+      <x:c r="D10" s="6"/>
+      <x:c r="E10" s="6" t="str">
+        <x:v>식이 질환규칙 없음</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="str">
+        <x:v>HEART_DISEASE</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>심장질환</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>NEEDS_SUBTYPE</x:v>
+      </x:c>
+      <x:c r="D11" s="6"/>
+      <x:c r="E11" s="6" t="str">
+        <x:v>기존 DX-06은 심장·뇌혈관을 묶고 수분 금지 사유가 심부전이므로 일괄 연결 보류</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>CEREBROVASCULAR_DISEASE</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>뇌혈관질환</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>NEEDS_SUBTYPE</x:v>
+      </x:c>
+      <x:c r="D12" s="6"/>
+      <x:c r="E12" s="6" t="str">
+        <x:v>기존 DX-06의 심부전 수분 금지를 그대로 적용하지 않음</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="6" t="str">
+        <x:v>CHRONIC_LUNG_DISEASE</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>천식 · 만성 폐질환</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>UNMAPPED</x:v>
+      </x:c>
+      <x:c r="D13" s="6"/>
+      <x:c r="E13" s="6" t="str">
+        <x:v>식이 질환규칙 없음</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>공개 프로토타입 &gt; 더보기 &gt; 내정보 &gt; 만성질환</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re43d8851d0f34a6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24337,10 +24763,368 @@
         <x:v>ANSWERED이면 필수. 같은 사용자·meal_date·meal_type·question_id·question_version의 마지막 유효 응답을 가리킨다. 이전 세션의 응답 재사용 가능; PENDING·CONDITIONAL_SKIP은 NULL</x:v>
       </x:c>
     </x:row>
+    <x:row r="275">
+      <x:c r="A275" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="B275" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C275" t="str">
+        <x:v>condition_code</x:v>
+      </x:c>
+      <x:c r="D275" t="str">
+        <x:v>화면 질환 코드</x:v>
+      </x:c>
+      <x:c r="E275" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="F275" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G275" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H275"/>
+      <x:c r="I275" t="str">
+        <x:v>공개 화면 선택지 12개만 허용</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="B276" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C276" t="str">
+        <x:v>display_name</x:v>
+      </x:c>
+      <x:c r="D276" t="str">
+        <x:v>화면 표시명</x:v>
+      </x:c>
+      <x:c r="E276" t="str">
+        <x:v>VARCHAR(50)</x:v>
+      </x:c>
+      <x:c r="F276" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G276"/>
+      <x:c r="H276"/>
+      <x:c r="I276"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="B277" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C277" t="str">
+        <x:v>diet_status</x:v>
+      </x:c>
+      <x:c r="D277" t="str">
+        <x:v>식이 연결 상태</x:v>
+      </x:c>
+      <x:c r="E277" t="str">
+        <x:v>ENUM</x:v>
+      </x:c>
+      <x:c r="F277" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G277"/>
+      <x:c r="H277" t="str">
+        <x:v>MAPPED,UNMAPPED,NEEDS_SUBTYPE</x:v>
+      </x:c>
+      <x:c r="I277" t="str">
+        <x:v>MAPPED만 자동 연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="B278" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C278" t="str">
+        <x:v>rule_id</x:v>
+      </x:c>
+      <x:c r="D278" t="str">
+        <x:v>식이 질환 규칙 ID</x:v>
+      </x:c>
+      <x:c r="E278" t="str">
+        <x:v>VARCHAR(10)</x:v>
+      </x:c>
+      <x:c r="F278" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="G278" t="str">
+        <x:v>FK→diet_disease_rule</x:v>
+      </x:c>
+      <x:c r="H278"/>
+      <x:c r="I278" t="str">
+        <x:v>MAPPED이면 필수, 나머지는 NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="B279" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C279" t="str">
+        <x:v>mapping_note</x:v>
+      </x:c>
+      <x:c r="D279" t="str">
+        <x:v>연결 판단 설명</x:v>
+      </x:c>
+      <x:c r="E279" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="F279" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G279"/>
+      <x:c r="H279"/>
+      <x:c r="I279"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="B280" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C280" t="str">
+        <x:v>source_ui</x:v>
+      </x:c>
+      <x:c r="D280" t="str">
+        <x:v>화면 출처</x:v>
+      </x:c>
+      <x:c r="E280" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="F280" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G280"/>
+      <x:c r="H280"/>
+      <x:c r="I280"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="str">
+        <x:v>user_condition_response</x:v>
+      </x:c>
+      <x:c r="B281" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C281" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="D281" t="str">
+        <x:v>사용자 ID</x:v>
+      </x:c>
+      <x:c r="E281" t="str">
+        <x:v>VARCHAR(64)</x:v>
+      </x:c>
+      <x:c r="F281" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G281" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H281"/>
+      <x:c r="I281"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="str">
+        <x:v>user_condition_response</x:v>
+      </x:c>
+      <x:c r="B282" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C282" t="str">
+        <x:v>revision</x:v>
+      </x:c>
+      <x:c r="D282" t="str">
+        <x:v>응답 리비전</x:v>
+      </x:c>
+      <x:c r="E282" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="F282" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G282" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H282"/>
+      <x:c r="I282" t="str">
+        <x:v>저장할 때마다 증가; 최신 리비전으로 현재 입력 판정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="str">
+        <x:v>user_condition_response</x:v>
+      </x:c>
+      <x:c r="B283" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C283" t="str">
+        <x:v>response_state</x:v>
+      </x:c>
+      <x:c r="D283" t="str">
+        <x:v>수동 입력 상태</x:v>
+      </x:c>
+      <x:c r="E283" t="str">
+        <x:v>ENUM</x:v>
+      </x:c>
+      <x:c r="F283" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G283"/>
+      <x:c r="H283" t="str">
+        <x:v>UNANSWERED,NONE,SELECTED</x:v>
+      </x:c>
+      <x:c r="I283" t="str">
+        <x:v>NONE은 사용자가 해당 없음 선택, UNANSWERED는 입력하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="str">
+        <x:v>user_condition_response</x:v>
+      </x:c>
+      <x:c r="B284" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C284" t="str">
+        <x:v>input_source</x:v>
+      </x:c>
+      <x:c r="D284" t="str">
+        <x:v>입력 출처</x:v>
+      </x:c>
+      <x:c r="E284" t="str">
+        <x:v>ENUM</x:v>
+      </x:c>
+      <x:c r="F284" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G284"/>
+      <x:c r="H284" t="str">
+        <x:v>SELF_REPORTED</x:v>
+      </x:c>
+      <x:c r="I284" t="str">
+        <x:v>진료정보 연동이나 의료진 진단으로 표시하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="str">
+        <x:v>user_condition_response</x:v>
+      </x:c>
+      <x:c r="B285" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C285" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="D285" t="str">
+        <x:v>저장 시각</x:v>
+      </x:c>
+      <x:c r="E285" t="str">
+        <x:v>TIMESTAMP WITH TIME ZONE</x:v>
+      </x:c>
+      <x:c r="F285" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G285"/>
+      <x:c r="H285"/>
+      <x:c r="I285"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" t="str">
+        <x:v>user_condition_selection</x:v>
+      </x:c>
+      <x:c r="B286" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C286" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="D286" t="str">
+        <x:v>사용자 ID</x:v>
+      </x:c>
+      <x:c r="E286" t="str">
+        <x:v>VARCHAR(64)</x:v>
+      </x:c>
+      <x:c r="F286" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G286" t="str">
+        <x:v>PK/FK→user_condition_response</x:v>
+      </x:c>
+      <x:c r="H286"/>
+      <x:c r="I286"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" t="str">
+        <x:v>user_condition_selection</x:v>
+      </x:c>
+      <x:c r="B287" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C287" t="str">
+        <x:v>revision</x:v>
+      </x:c>
+      <x:c r="D287" t="str">
+        <x:v>응답 리비전</x:v>
+      </x:c>
+      <x:c r="E287" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="F287" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G287" t="str">
+        <x:v>PK/FK→user_condition_response</x:v>
+      </x:c>
+      <x:c r="H287"/>
+      <x:c r="I287" t="str">
+        <x:v>응답 상태 SELECTED인 리비전의 선택 행만 저장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" t="str">
+        <x:v>user_condition_selection</x:v>
+      </x:c>
+      <x:c r="B288" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C288" t="str">
+        <x:v>condition_code</x:v>
+      </x:c>
+      <x:c r="D288" t="str">
+        <x:v>화면 질환 코드</x:v>
+      </x:c>
+      <x:c r="E288" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="F288" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="G288" t="str">
+        <x:v>PK/FK→profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="H288"/>
+      <x:c r="I288" t="str">
+        <x:v>선택한 12개 코드 중 하나</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29c3ed4a68f84108"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7e54c41529d4ee7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24730,13 +25514,27 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="1"/>
-      <x:c r="B17" s="1"/>
-      <x:c r="C17" s="1"/>
-      <x:c r="D17" s="1"/>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="1"/>
+      <x:c r="A17" s="1" t="str">
+        <x:v>I-23</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="str">
+        <x:v>profile_condition_diet_map</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="str">
+        <x:v>공개 프로토타입 &gt; 내정보 &gt; 만성질환 12개</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="str">
+        <x:v>수동 선택 12개 중 7개는 식이 규칙이 없거나 심장·뇌혈관을 세부형 없이 공통 DX-06으로 묶어 안전하게 연결할 수 없음</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="str">
+        <x:v>비만·역류병·통풍·갑상선·폐질환의 식이 규칙과 심장·뇌혈관 세부형/수분 금지 범위를 확정. 확정 전에는 입력만 보존하고 자동 식이 반영 보류</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="1"/>
@@ -24768,7 +25566,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R503f72e2ee814e3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R108a99fec1344369"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25055,7 +25853,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55b93e8e1cca474e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68da69a14bff4e88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25647,7 +26445,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd58a54194af34742"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa4b1cac6971434a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32385,7 +33183,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08eb7d8484d64bde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9e79ef0d8404204"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37997,7 +38795,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2253710aa3f146bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66561d4a321d440a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38527,7 +39325,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cd72ca3764d4f52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R092235b653344fc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>